--- a/input/schedule.xlsx
+++ b/input/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iimshillong-my.sharepoint.com/personal/epgp_iimshillong_ac_in/Documents/DATA/PGPEx 2 (Ken)/PGPEx 2026/Term IV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1962" documentId="13_ncr:1_{A469BD59-4BB5-42CB-8559-68E6661E9BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E35F7FD3-437B-4F9F-AF4B-E2BB4D93A249}"/>
+  <xr:revisionPtr revIDLastSave="2014" documentId="13_ncr:1_{A469BD59-4BB5-42CB-8559-68E6661E9BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527986AC-10AD-431B-B321-21D3E0E4B2BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{5F88A533-2550-461E-80E1-A34C7E95548C}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="252">
   <si>
     <t>Indian Institute of Management Shillong</t>
   </si>
@@ -923,9 +923,6 @@
     <t xml:space="preserve">CM </t>
   </si>
   <si>
-    <t xml:space="preserve">SM </t>
-  </si>
-  <si>
     <t>PGPEx (2026-27) Term IV</t>
   </si>
   <si>
@@ -1062,6 +1059,12 @@
   </si>
   <si>
     <t>Prof. Pradeep  Rathore</t>
+  </si>
+  <si>
+    <t>Services Marketing - SMKTG</t>
+  </si>
+  <si>
+    <t>SMKTG</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1074,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1296,6 +1299,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1842,7 +1860,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2224,33 +2242,15 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2275,15 +2275,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="6" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2323,13 +2344,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2529,9 +2544,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2831,10 +2843,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3170,44 +3178,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
     </row>
     <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3229,22 +3237,22 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="189" t="s">
+      <c r="G5" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="177"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4170,7 +4178,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="154" t="s">
+      <c r="A32" s="155" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="44">
@@ -4179,95 +4187,95 @@
       <c r="C32" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="190" t="s">
+      <c r="D32" s="189" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="190"/>
-      <c r="F32" s="190"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="190"/>
-      <c r="J32" s="191"/>
+      <c r="E32" s="189"/>
+      <c r="F32" s="189"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="190"/>
     </row>
     <row r="33" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="154"/>
+      <c r="A33" s="155"/>
       <c r="B33" s="44">
         <v>46357</v>
       </c>
       <c r="C33" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="192"/>
-      <c r="E33" s="192"/>
-      <c r="F33" s="192"/>
-      <c r="G33" s="192"/>
-      <c r="H33" s="192"/>
-      <c r="I33" s="192"/>
-      <c r="J33" s="193"/>
+      <c r="D33" s="191"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="191"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="192"/>
     </row>
     <row r="34" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="154"/>
+      <c r="A34" s="155"/>
       <c r="B34" s="44">
         <v>46358</v>
       </c>
       <c r="C34" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="192"/>
-      <c r="E34" s="192"/>
-      <c r="F34" s="192"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
-      <c r="I34" s="192"/>
-      <c r="J34" s="193"/>
+      <c r="D34" s="191"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="192"/>
     </row>
     <row r="35" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="154"/>
+      <c r="A35" s="155"/>
       <c r="B35" s="44">
         <v>46359</v>
       </c>
       <c r="C35" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-      <c r="I35" s="192"/>
-      <c r="J35" s="193"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="191"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="192"/>
     </row>
     <row r="36" spans="1:10" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="154"/>
+      <c r="A36" s="155"/>
       <c r="B36" s="44">
         <v>46360</v>
       </c>
       <c r="C36" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="192"/>
-      <c r="E36" s="192"/>
-      <c r="F36" s="192"/>
-      <c r="G36" s="192"/>
-      <c r="H36" s="192"/>
-      <c r="I36" s="192"/>
-      <c r="J36" s="193"/>
+      <c r="D36" s="191"/>
+      <c r="E36" s="191"/>
+      <c r="F36" s="191"/>
+      <c r="G36" s="191"/>
+      <c r="H36" s="191"/>
+      <c r="I36" s="191"/>
+      <c r="J36" s="192"/>
     </row>
     <row r="37" spans="1:10" s="4" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="155"/>
+      <c r="A37" s="156"/>
       <c r="B37" s="44">
         <v>46361</v>
       </c>
       <c r="C37" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="194"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="194"/>
-      <c r="G37" s="194"/>
-      <c r="H37" s="194"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="195"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="194"/>
     </row>
     <row r="38" spans="1:10" s="4" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
@@ -4282,30 +4290,30 @@
       <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="196" t="s">
+      <c r="A39" s="195" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="197"/>
-      <c r="C39" s="197"/>
-      <c r="D39" s="197"/>
-      <c r="E39" s="197"/>
-      <c r="F39" s="197"/>
-      <c r="G39" s="197"/>
-      <c r="H39" s="197"/>
-      <c r="I39" s="198" t="s">
+      <c r="B39" s="196"/>
+      <c r="C39" s="196"/>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="196"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="196"/>
+      <c r="I39" s="197" t="s">
         <v>38</v>
       </c>
-      <c r="J39" s="199"/>
+      <c r="J39" s="198"/>
     </row>
     <row r="40" spans="1:10" s="22" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="200" t="s">
+      <c r="B40" s="199" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="200"/>
-      <c r="D40" s="200"/>
+      <c r="C40" s="199"/>
+      <c r="D40" s="199"/>
       <c r="E40" s="21" t="s">
         <v>41</v>
       </c>
@@ -4329,11 +4337,11 @@
       <c r="A41" s="92" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="186" t="s">
+      <c r="B41" s="185" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="186"/>
-      <c r="D41" s="186"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="185"/>
       <c r="E41" s="97" t="s">
         <v>183</v>
       </c>
@@ -4346,20 +4354,20 @@
       <c r="H41" s="106">
         <v>61</v>
       </c>
-      <c r="I41" s="187" t="s">
+      <c r="I41" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="188"/>
+      <c r="J41" s="187"/>
     </row>
     <row r="42" spans="1:10" s="22" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="181" t="s">
+      <c r="B42" s="180" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="181"/>
-      <c r="D42" s="181"/>
+      <c r="C42" s="180"/>
+      <c r="D42" s="180"/>
       <c r="E42" s="96" t="s">
         <v>49</v>
       </c>
@@ -4383,11 +4391,11 @@
       <c r="A43" s="93" t="s">
         <v>154</v>
       </c>
-      <c r="B43" s="181" t="s">
+      <c r="B43" s="180" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="181"/>
-      <c r="D43" s="181"/>
+      <c r="C43" s="180"/>
+      <c r="D43" s="180"/>
       <c r="E43" s="96" t="s">
         <v>190</v>
       </c>
@@ -4400,20 +4408,20 @@
       <c r="H43" s="107">
         <v>60</v>
       </c>
-      <c r="I43" s="182" t="s">
+      <c r="I43" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="183"/>
+      <c r="J43" s="182"/>
     </row>
     <row r="44" spans="1:10" s="22" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="181" t="s">
+      <c r="B44" s="180" t="s">
         <v>165</v>
       </c>
-      <c r="C44" s="181"/>
-      <c r="D44" s="181"/>
+      <c r="C44" s="180"/>
+      <c r="D44" s="180"/>
       <c r="E44" s="96" t="s">
         <v>184</v>
       </c>
@@ -4437,11 +4445,11 @@
       <c r="A45" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="181" t="s">
+      <c r="B45" s="180" t="s">
         <v>166</v>
       </c>
-      <c r="C45" s="181"/>
-      <c r="D45" s="181"/>
+      <c r="C45" s="180"/>
+      <c r="D45" s="180"/>
       <c r="E45" s="96" t="s">
         <v>56</v>
       </c>
@@ -4454,20 +4462,20 @@
       <c r="H45" s="107">
         <v>71</v>
       </c>
-      <c r="I45" s="182" t="s">
+      <c r="I45" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J45" s="183"/>
+      <c r="J45" s="182"/>
     </row>
     <row r="46" spans="1:10" s="22" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="93" t="s">
         <v>155</v>
       </c>
-      <c r="B46" s="181" t="s">
+      <c r="B46" s="180" t="s">
         <v>167</v>
       </c>
-      <c r="C46" s="181"/>
-      <c r="D46" s="181"/>
+      <c r="C46" s="180"/>
+      <c r="D46" s="180"/>
       <c r="E46" s="96" t="s">
         <v>185</v>
       </c>
@@ -4480,20 +4488,20 @@
       <c r="H46" s="107">
         <v>60</v>
       </c>
-      <c r="I46" s="182" t="s">
+      <c r="I46" s="181" t="s">
         <v>67</v>
       </c>
-      <c r="J46" s="183"/>
+      <c r="J46" s="182"/>
     </row>
     <row r="47" spans="1:10" s="22" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="181" t="s">
+      <c r="B47" s="180" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="181"/>
-      <c r="D47" s="181"/>
+      <c r="C47" s="180"/>
+      <c r="D47" s="180"/>
       <c r="E47" s="96" t="s">
         <v>60</v>
       </c>
@@ -4506,20 +4514,20 @@
       <c r="H47" s="103">
         <v>71</v>
       </c>
-      <c r="I47" s="182" t="s">
+      <c r="I47" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J47" s="183"/>
+      <c r="J47" s="182"/>
     </row>
     <row r="48" spans="1:10" s="22" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="B48" s="181" t="s">
+      <c r="B48" s="180" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="181"/>
-      <c r="D48" s="181"/>
+      <c r="C48" s="180"/>
+      <c r="D48" s="180"/>
       <c r="E48" s="96" t="s">
         <v>73</v>
       </c>
@@ -4543,11 +4551,11 @@
       <c r="A49" s="94" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="181" t="s">
+      <c r="B49" s="180" t="s">
         <v>170</v>
       </c>
-      <c r="C49" s="181"/>
-      <c r="D49" s="181"/>
+      <c r="C49" s="180"/>
+      <c r="D49" s="180"/>
       <c r="E49" s="96" t="s">
         <v>186</v>
       </c>
@@ -4560,20 +4568,20 @@
       <c r="H49" s="107">
         <v>60</v>
       </c>
-      <c r="I49" s="182" t="s">
+      <c r="I49" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J49" s="183"/>
+      <c r="J49" s="182"/>
     </row>
     <row r="50" spans="1:10" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="181" t="s">
+      <c r="B50" s="180" t="s">
         <v>171</v>
       </c>
-      <c r="C50" s="181"/>
-      <c r="D50" s="181"/>
+      <c r="C50" s="180"/>
+      <c r="D50" s="180"/>
       <c r="E50" s="96" t="s">
         <v>76</v>
       </c>
@@ -4586,20 +4594,20 @@
       <c r="H50" s="103">
         <v>71</v>
       </c>
-      <c r="I50" s="182" t="s">
+      <c r="I50" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J50" s="183"/>
+      <c r="J50" s="182"/>
     </row>
     <row r="51" spans="1:10" s="22" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="B51" s="181" t="s">
+      <c r="B51" s="180" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="181"/>
-      <c r="D51" s="181"/>
+      <c r="C51" s="180"/>
+      <c r="D51" s="180"/>
       <c r="E51" s="96" t="s">
         <v>79</v>
       </c>
@@ -4623,11 +4631,11 @@
       <c r="A52" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="181" t="s">
+      <c r="B52" s="180" t="s">
         <v>173</v>
       </c>
-      <c r="C52" s="181"/>
-      <c r="D52" s="181"/>
+      <c r="C52" s="180"/>
+      <c r="D52" s="180"/>
       <c r="E52" s="96" t="s">
         <v>85</v>
       </c>
@@ -4640,20 +4648,20 @@
       <c r="H52" s="103">
         <v>70</v>
       </c>
-      <c r="I52" s="182" t="s">
+      <c r="I52" s="181" t="s">
         <v>57</v>
       </c>
-      <c r="J52" s="183"/>
+      <c r="J52" s="182"/>
     </row>
     <row r="53" spans="1:10" s="22" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="B53" s="181" t="s">
+      <c r="B53" s="180" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="181"/>
-      <c r="D53" s="181"/>
+      <c r="C53" s="180"/>
+      <c r="D53" s="180"/>
       <c r="E53" s="96" t="s">
         <v>192</v>
       </c>
@@ -4666,20 +4674,20 @@
       <c r="H53" s="103">
         <v>71</v>
       </c>
-      <c r="I53" s="182" t="s">
+      <c r="I53" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J53" s="183"/>
+      <c r="J53" s="182"/>
     </row>
     <row r="54" spans="1:10" s="22" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="93" t="s">
         <v>158</v>
       </c>
-      <c r="B54" s="181" t="s">
+      <c r="B54" s="180" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="181"/>
-      <c r="D54" s="181"/>
+      <c r="C54" s="180"/>
+      <c r="D54" s="180"/>
       <c r="E54" s="96" t="s">
         <v>91</v>
       </c>
@@ -4703,11 +4711,11 @@
       <c r="A55" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="181" t="s">
+      <c r="B55" s="180" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="181"/>
-      <c r="D55" s="181"/>
+      <c r="C55" s="180"/>
+      <c r="D55" s="180"/>
       <c r="E55" s="96" t="s">
         <v>82</v>
       </c>
@@ -4720,20 +4728,20 @@
       <c r="H55" s="103">
         <v>70</v>
       </c>
-      <c r="I55" s="182" t="s">
+      <c r="I55" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J55" s="183"/>
+      <c r="J55" s="182"/>
     </row>
     <row r="56" spans="1:10" s="22" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="181" t="s">
+      <c r="B56" s="180" t="s">
         <v>177</v>
       </c>
-      <c r="C56" s="181"/>
-      <c r="D56" s="181"/>
+      <c r="C56" s="180"/>
+      <c r="D56" s="180"/>
       <c r="E56" s="96" t="s">
         <v>94</v>
       </c>
@@ -4746,20 +4754,20 @@
       <c r="H56" s="103">
         <v>70</v>
       </c>
-      <c r="I56" s="184" t="s">
+      <c r="I56" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="J56" s="185"/>
+      <c r="J56" s="184"/>
     </row>
     <row r="57" spans="1:10" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="181" t="s">
+      <c r="B57" s="180" t="s">
         <v>178</v>
       </c>
-      <c r="C57" s="181"/>
-      <c r="D57" s="181"/>
+      <c r="C57" s="180"/>
+      <c r="D57" s="180"/>
       <c r="E57" s="96" t="s">
         <v>187</v>
       </c>
@@ -4783,11 +4791,11 @@
       <c r="A58" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="181" t="s">
+      <c r="B58" s="180" t="s">
         <v>179</v>
       </c>
-      <c r="C58" s="181"/>
-      <c r="D58" s="181"/>
+      <c r="C58" s="180"/>
+      <c r="D58" s="180"/>
       <c r="E58" s="96" t="s">
         <v>198</v>
       </c>
@@ -4800,20 +4808,20 @@
       <c r="H58" s="103">
         <v>60</v>
       </c>
-      <c r="I58" s="182" t="s">
+      <c r="I58" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J58" s="183"/>
+      <c r="J58" s="182"/>
     </row>
     <row r="59" spans="1:10" s="22" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="B59" s="181" t="s">
+      <c r="B59" s="180" t="s">
         <v>180</v>
       </c>
-      <c r="C59" s="181"/>
-      <c r="D59" s="181"/>
+      <c r="C59" s="180"/>
+      <c r="D59" s="180"/>
       <c r="E59" s="96" t="s">
         <v>191</v>
       </c>
@@ -4826,20 +4834,20 @@
       <c r="H59" s="103">
         <v>60</v>
       </c>
-      <c r="I59" s="182" t="s">
+      <c r="I59" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="J59" s="183"/>
+      <c r="J59" s="182"/>
     </row>
     <row r="60" spans="1:10" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="181" t="s">
+      <c r="B60" s="180" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="181"/>
-      <c r="D60" s="181"/>
+      <c r="C60" s="180"/>
+      <c r="D60" s="180"/>
       <c r="E60" s="96" t="s">
         <v>188</v>
       </c>
@@ -4863,11 +4871,11 @@
       <c r="A61" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="B61" s="178" t="s">
+      <c r="B61" s="177" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="178"/>
-      <c r="D61" s="178"/>
+      <c r="C61" s="177"/>
+      <c r="D61" s="177"/>
       <c r="E61" s="98" t="s">
         <v>189</v>
       </c>
@@ -4880,10 +4888,10 @@
       <c r="H61" s="108">
         <v>57</v>
       </c>
-      <c r="I61" s="179" t="s">
+      <c r="I61" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="J61" s="180"/>
+      <c r="J61" s="179"/>
     </row>
     <row r="66" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -4962,105 +4970,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
+      <c r="A2" s="172" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="A3" s="172"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
     </row>
     <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="174" t="s">
-        <v>246</v>
-      </c>
-      <c r="H4" s="175"/>
-      <c r="I4" s="176"/>
+      <c r="G4" s="173" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="174"/>
+      <c r="I4" s="175"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
     </row>
     <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="177"/>
-      <c r="B6" s="177"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="134" t="s">
+      <c r="J7" s="147" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="169" t="s">
+      <c r="A8" s="168" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="44">
@@ -5069,122 +5077,125 @@
       <c r="C8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="141" t="s">
+      <c r="D8" s="135"/>
+      <c r="E8" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H8" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="141" t="s">
+      <c r="H8" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="J8" s="135"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="169"/>
+      <c r="A9" s="168"/>
       <c r="B9" s="44">
         <v>46274</v>
       </c>
       <c r="C9" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E9" s="139"/>
-      <c r="F9" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G9" s="136"/>
-      <c r="H9" s="139" t="s">
+      <c r="E9" s="145" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G9" s="133"/>
+      <c r="H9" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="I9" s="139" t="s">
+      <c r="I9" s="135" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="81"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="169"/>
+      <c r="A10" s="168"/>
       <c r="B10" s="44">
         <v>46275</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G10" s="141" t="s">
+      <c r="D10" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="G10" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="139" t="s">
+      <c r="H10" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="J10" s="139"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="169"/>
+      <c r="A11" s="168"/>
       <c r="B11" s="44">
         <v>46276</v>
       </c>
       <c r="C11" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="139" t="s">
+      <c r="D11" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="F11" s="139" t="s">
+      <c r="F11" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="139" t="s">
+      <c r="G11" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="H11" s="139" t="s">
+      <c r="H11" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="170"/>
+      <c r="A12" s="169"/>
       <c r="B12" s="44">
         <v>46277</v>
       </c>
       <c r="C12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="139" t="s">
+      <c r="D12" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="F12" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="137"/>
+      <c r="F12" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="81"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="134"/>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
@@ -5194,16 +5205,16 @@
       <c r="C13" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="142"/>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="155" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="44">
@@ -5212,7 +5223,7 @@
       <c r="C14" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="166" t="s">
+      <c r="D14" s="167" t="s">
         <v>149</v>
       </c>
       <c r="E14" s="167"/>
@@ -5220,129 +5231,129 @@
       <c r="G14" s="167"/>
       <c r="H14" s="167"/>
       <c r="I14" s="167"/>
-      <c r="J14" s="168"/>
+      <c r="J14" s="167"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="154"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="44">
         <v>46280</v>
       </c>
       <c r="C15" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="141" t="s">
+      <c r="D15" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="141"/>
-      <c r="F15" s="139" t="s">
+      <c r="E15" s="135"/>
+      <c r="F15" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="G15" s="143" t="s">
-        <v>210</v>
-      </c>
-      <c r="H15" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
+      <c r="G15" s="137" t="s">
+        <v>209</v>
+      </c>
+      <c r="H15" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="44">
         <v>46281</v>
       </c>
       <c r="C16" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="141" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G16" s="144"/>
-      <c r="H16" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="139" t="s">
+      <c r="D16" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="135" t="s">
+        <v>205</v>
+      </c>
+      <c r="F16" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="G16" s="138"/>
+      <c r="H16" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="J16" s="139"/>
+      <c r="J16" s="135"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="154"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="44">
         <v>46282</v>
       </c>
       <c r="C17" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="139" t="s">
+      <c r="D17" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E17" s="141"/>
+      <c r="E17" s="135"/>
       <c r="F17" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G17" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="139" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="I17" s="139"/>
-      <c r="J17" s="139"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="154"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="44">
         <v>46283</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="139" t="s">
+      <c r="D18" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="139"/>
-      <c r="H18" s="141" t="s">
+      <c r="E18" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="139"/>
-      <c r="J18" s="139"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="154"/>
+      <c r="A19" s="155"/>
       <c r="B19" s="44">
         <v>46284</v>
       </c>
       <c r="C19" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="139" t="s">
+      <c r="D19" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G19" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="H19" s="139"/>
-      <c r="I19" s="139"/>
-      <c r="J19" s="139"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
@@ -5352,16 +5363,16 @@
       <c r="C20" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="145"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="142"/>
-      <c r="J20" s="142"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="154" t="s">
+      <c r="A21" s="155" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="44">
@@ -5370,141 +5381,141 @@
       <c r="C21" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="139" t="s">
+      <c r="D21" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
-      <c r="G21" s="139"/>
-      <c r="H21" s="141" t="s">
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="141"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="154"/>
+      <c r="A22" s="155"/>
       <c r="B22" s="44">
         <v>46287</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="139" t="s">
+      <c r="D22" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="E22" s="135" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G22" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="139" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="141"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="154"/>
+      <c r="A23" s="155"/>
       <c r="B23" s="44">
         <v>46288</v>
       </c>
       <c r="C23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="141" t="s">
+      <c r="D23" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="E23" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="138" t="s">
-        <v>240</v>
-      </c>
-      <c r="G23" s="144"/>
-      <c r="H23" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="141"/>
+      <c r="E23" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="149" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" s="138"/>
+      <c r="H23" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="154"/>
+      <c r="A24" s="155"/>
       <c r="B24" s="44">
         <v>46289</v>
       </c>
       <c r="C24" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="139" t="s">
+      <c r="D24" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E24" s="139" t="s">
+      <c r="E24" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="H24" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="154"/>
+      <c r="A25" s="155"/>
       <c r="B25" s="44">
         <v>46290</v>
       </c>
       <c r="C25" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139" t="s">
+      <c r="D25" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="154"/>
+      <c r="A26" s="155"/>
       <c r="B26" s="44">
         <v>46291</v>
       </c>
       <c r="C26" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="139" t="s">
+      <c r="D26" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="139"/>
-      <c r="J26" s="146"/>
+      <c r="G26" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="135"/>
+      <c r="J26" s="140"/>
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
@@ -5514,22 +5525,22 @@
       <c r="C27" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
+      <c r="D27" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="136"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="154" t="s">
+      <c r="A28" s="155" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="44">
@@ -5538,123 +5549,125 @@
       <c r="C28" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="139" t="s">
+      <c r="D28" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E28" s="139" t="s">
+      <c r="E28" s="135" t="s">
         <v>202</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G28" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" s="141" t="s">
+        <v>240</v>
+      </c>
+      <c r="G28" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="135" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="154"/>
+      <c r="A29" s="155"/>
       <c r="B29" s="44">
         <v>46294</v>
       </c>
       <c r="C29" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="139" t="s">
+      <c r="D29" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="E29" s="139"/>
-      <c r="F29" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G29" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="H29" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="143" t="s">
+      <c r="E29" s="150" t="s">
+        <v>239</v>
+      </c>
+      <c r="F29" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="H29" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="137" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="154"/>
+      <c r="A30" s="155"/>
       <c r="B30" s="44">
         <v>46295</v>
       </c>
       <c r="C30" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="139" t="s">
+      <c r="D30" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E30" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="139" t="s">
-        <v>207</v>
-      </c>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="139" t="s">
+      <c r="E30" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="135" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="135" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="154"/>
+      <c r="A31" s="155"/>
       <c r="B31" s="44">
         <v>46296</v>
       </c>
       <c r="C31" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="139" t="s">
+      <c r="D31" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="E31" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="F31" s="139" t="s">
+      <c r="F31" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="139" t="s">
+      <c r="G31" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="J31" s="139" t="s">
+      <c r="J31" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="154"/>
+      <c r="A32" s="155"/>
       <c r="B32" s="44">
         <v>46297</v>
       </c>
       <c r="C32" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="166" t="s">
+      <c r="D32" s="167" t="s">
         <v>150</v>
       </c>
       <c r="E32" s="167"/>
@@ -5662,32 +5675,28 @@
       <c r="G32" s="167"/>
       <c r="H32" s="167"/>
       <c r="I32" s="167"/>
-      <c r="J32" s="168"/>
+      <c r="J32" s="167"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="154"/>
+      <c r="A33" s="155"/>
       <c r="B33" s="44">
         <v>46298</v>
       </c>
       <c r="C33" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="E33" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="G33" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="H33" s="139" t="s">
-        <v>213</v>
-      </c>
-      <c r="I33" s="139" t="s">
+      <c r="D33" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135" t="s">
+        <v>212</v>
+      </c>
+      <c r="I33" s="135" t="s">
         <v>27</v>
       </c>
       <c r="J33" s="81"/>
@@ -5700,187 +5709,177 @@
       <c r="C34" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="142"/>
-      <c r="E34" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="H34" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="I34" s="142"/>
-      <c r="J34" s="142"/>
+      <c r="D34" s="136"/>
+      <c r="E34" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="136"/>
+      <c r="H34" s="136"/>
+      <c r="I34" s="136"/>
+      <c r="J34" s="136"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="154" t="s">
+      <c r="A35" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="151">
+      <c r="B35" s="144">
         <v>46300</v>
       </c>
       <c r="C35" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="E35" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="F35" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="G35" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="H35" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="I35" s="139"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="G35" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
       <c r="J35" s="81"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="154"/>
+      <c r="A36" s="155"/>
       <c r="B36" s="44">
         <v>46301</v>
       </c>
       <c r="C36" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="139" t="s">
+      <c r="D36" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="E36" s="139" t="s">
+      <c r="E36" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G36" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="139" t="s">
+      <c r="F36" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G36" s="145" t="s">
+        <v>240</v>
+      </c>
+      <c r="H36" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="I36" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="J36" s="139" t="s">
+      <c r="I36" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="J36" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="154"/>
+      <c r="A37" s="155"/>
       <c r="B37" s="44">
         <v>46302</v>
       </c>
       <c r="C37" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="141" t="s">
+      <c r="D37" s="150" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G37" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I37" s="141" t="s">
-        <v>211</v>
-      </c>
-      <c r="J37" s="139" t="s">
+      <c r="F37" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="J37" s="135" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="154"/>
+      <c r="A38" s="155"/>
       <c r="B38" s="44">
         <v>46303</v>
       </c>
       <c r="C38" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" s="139" t="s">
+      <c r="D38" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="139" t="s">
+      <c r="H38" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="I38" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J38" s="139" t="s">
+      <c r="I38" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="154"/>
+      <c r="A39" s="155"/>
       <c r="B39" s="44">
         <v>46304</v>
       </c>
       <c r="C39" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="139" t="s">
+      <c r="D39" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139" t="s">
+      <c r="E39" s="135"/>
+      <c r="F39" s="135"/>
+      <c r="G39" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="H39" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J39" s="139" t="s">
+      <c r="H39" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="154"/>
+      <c r="A40" s="155"/>
       <c r="B40" s="44">
         <v>46305</v>
       </c>
       <c r="C40" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="E40" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G40" s="141" t="s">
+      <c r="D40" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H40" s="139"/>
+      <c r="H40" s="135"/>
       <c r="I40" s="81"/>
       <c r="J40" s="81"/>
     </row>
@@ -5892,16 +5891,16 @@
       <c r="C41" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="142"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="142"/>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
+      <c r="D41" s="136"/>
+      <c r="E41" s="136"/>
+      <c r="F41" s="136"/>
+      <c r="G41" s="136"/>
+      <c r="H41" s="136"/>
+      <c r="I41" s="136"/>
+      <c r="J41" s="136"/>
     </row>
     <row r="42" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="154" t="s">
+      <c r="A42" s="155" t="s">
         <v>26</v>
       </c>
       <c r="B42" s="44">
@@ -5910,149 +5909,137 @@
       <c r="C42" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="139" t="s">
+      <c r="D42" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="135" t="s">
         <v>196</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G42" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="139"/>
-      <c r="J42" s="139"/>
+        <v>240</v>
+      </c>
+      <c r="G42" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="H42" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="135"/>
+      <c r="J42" s="135"/>
     </row>
     <row r="43" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="154"/>
+      <c r="A43" s="155"/>
       <c r="B43" s="44">
         <v>46308</v>
       </c>
       <c r="C43" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="139" t="s">
+      <c r="D43" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="E43" s="140" t="s">
+      <c r="E43" s="137" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" s="137" t="s">
+        <v>208</v>
+      </c>
+      <c r="G43" s="135" t="s">
         <v>209</v>
       </c>
-      <c r="F43" s="140" t="s">
-        <v>209</v>
-      </c>
-      <c r="G43" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="H43" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="139"/>
-      <c r="J43" s="139" t="s">
-        <v>204</v>
-      </c>
+      <c r="H43" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="135"/>
+      <c r="J43" s="135"/>
     </row>
     <row r="44" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="154"/>
+      <c r="A44" s="155"/>
       <c r="B44" s="44">
         <v>46309</v>
       </c>
       <c r="C44" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="139" t="s">
+      <c r="D44" s="150" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="F44" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G44" s="144"/>
-      <c r="H44" s="139" t="s">
+      <c r="F44" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44" s="138"/>
+      <c r="H44" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="I44" s="139"/>
-      <c r="J44" s="139" t="s">
-        <v>204</v>
-      </c>
+      <c r="I44" s="135"/>
+      <c r="J44" s="135"/>
     </row>
     <row r="45" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="154"/>
+      <c r="A45" s="155"/>
       <c r="B45" s="44">
         <v>46310</v>
       </c>
       <c r="C45" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="139"/>
-      <c r="E45" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="F45" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" s="139" t="s">
+      <c r="D45" s="135"/>
+      <c r="E45" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="H45" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I45" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="J45" s="139"/>
+      <c r="H45" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="135"/>
+      <c r="J45" s="135"/>
     </row>
     <row r="46" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="154"/>
+      <c r="A46" s="155"/>
       <c r="B46" s="44">
         <v>46311</v>
       </c>
       <c r="C46" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="141" t="s">
+      <c r="D46" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="139" t="s">
+      <c r="E46" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="F46" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G46" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" s="139" t="s">
-        <v>204</v>
-      </c>
+      <c r="F46" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="135"/>
       <c r="I46" s="81"/>
       <c r="J46" s="81"/>
     </row>
     <row r="47" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="154"/>
+      <c r="A47" s="155"/>
       <c r="B47" s="44">
         <v>46312</v>
       </c>
       <c r="C47" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="146"/>
-      <c r="E47" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="F47" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="139"/>
-      <c r="H47" s="139"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="135"/>
+      <c r="F47" s="135"/>
+      <c r="G47" s="135"/>
+      <c r="H47" s="135"/>
+      <c r="I47" s="141"/>
+      <c r="J47" s="141"/>
     </row>
     <row r="48" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
@@ -6064,20 +6051,16 @@
       <c r="C48" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="142"/>
-      <c r="E48" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="F48" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="142"/>
-      <c r="H48" s="142"/>
-      <c r="I48" s="142"/>
-      <c r="J48" s="142"/>
+      <c r="D48" s="136"/>
+      <c r="E48" s="136"/>
+      <c r="F48" s="136"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="136"/>
+      <c r="I48" s="136"/>
+      <c r="J48" s="136"/>
     </row>
     <row r="49" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="154" t="s">
+      <c r="A49" s="155" t="s">
         <v>28</v>
       </c>
       <c r="B49" s="44">
@@ -6086,7 +6069,7 @@
       <c r="C49" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="166" t="s">
+      <c r="D49" s="167" t="s">
         <v>151</v>
       </c>
       <c r="E49" s="167"/>
@@ -6094,17 +6077,17 @@
       <c r="G49" s="167"/>
       <c r="H49" s="167"/>
       <c r="I49" s="167"/>
-      <c r="J49" s="168"/>
+      <c r="J49" s="167"/>
     </row>
     <row r="50" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="154"/>
+      <c r="A50" s="155"/>
       <c r="B50" s="44">
         <v>46315</v>
       </c>
       <c r="C50" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="166" t="s">
+      <c r="D50" s="167" t="s">
         <v>151</v>
       </c>
       <c r="E50" s="167"/>
@@ -6112,105 +6095,105 @@
       <c r="G50" s="167"/>
       <c r="H50" s="167"/>
       <c r="I50" s="167"/>
-      <c r="J50" s="168"/>
+      <c r="J50" s="167"/>
     </row>
     <row r="51" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="154"/>
+      <c r="A51" s="155"/>
       <c r="B51" s="44">
         <v>46316</v>
       </c>
       <c r="C51" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="139" t="s">
+      <c r="D51" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E51" s="139" t="s">
-        <v>242</v>
-      </c>
-      <c r="F51" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="G51" s="144"/>
-      <c r="H51" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I51" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J51" s="139"/>
+      <c r="E51" s="135" t="s">
+        <v>241</v>
+      </c>
+      <c r="F51" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="G51" s="138"/>
+      <c r="H51" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="135"/>
     </row>
     <row r="52" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="154"/>
+      <c r="A52" s="155"/>
       <c r="B52" s="44">
         <v>46317</v>
       </c>
       <c r="C52" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="139" t="s">
+      <c r="D52" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="E52" s="139" t="s">
+      <c r="E52" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="F52" s="139" t="s">
+      <c r="F52" s="135" t="s">
         <v>203</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="H52" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I52" s="139"/>
-      <c r="J52" s="141"/>
+        <v>240</v>
+      </c>
+      <c r="H52" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" s="135"/>
+      <c r="J52" s="135"/>
     </row>
     <row r="53" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="154"/>
+      <c r="A53" s="155"/>
       <c r="B53" s="44">
         <v>46318</v>
       </c>
       <c r="C53" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="139" t="s">
+      <c r="D53" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="E53" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="F53" s="150" t="s">
-        <v>240</v>
-      </c>
-      <c r="G53" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="H53" s="139" t="s">
+      <c r="E53" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="F53" s="151" t="s">
+        <v>239</v>
+      </c>
+      <c r="G53" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="I53" s="139"/>
-      <c r="J53" s="139"/>
+      <c r="I53" s="135"/>
+      <c r="J53" s="135"/>
     </row>
     <row r="54" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="154"/>
+      <c r="A54" s="155"/>
       <c r="B54" s="44">
         <v>46319</v>
       </c>
       <c r="C54" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="143" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="143" t="s">
-        <v>209</v>
+      <c r="D54" s="137" t="s">
+        <v>208</v>
+      </c>
+      <c r="E54" s="137" t="s">
+        <v>208</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="81"/>
-      <c r="H54" s="146"/>
-      <c r="I54" s="139"/>
-      <c r="J54" s="139"/>
+      <c r="H54" s="140"/>
+      <c r="I54" s="135"/>
+      <c r="J54" s="135"/>
     </row>
     <row r="55" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
@@ -6220,16 +6203,16 @@
       <c r="C55" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
+      <c r="D55" s="136"/>
+      <c r="E55" s="136"/>
+      <c r="F55" s="136"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="136"/>
+      <c r="J55" s="136"/>
     </row>
     <row r="56" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="154" t="s">
+      <c r="A56" s="155" t="s">
         <v>30</v>
       </c>
       <c r="B56" s="44">
@@ -6238,149 +6221,149 @@
       <c r="C56" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="139" t="s">
+      <c r="D56" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="E56" s="143" t="s">
-        <v>247</v>
-      </c>
-      <c r="F56" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G56" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="139" t="s">
+      <c r="E56" s="137" t="s">
+        <v>246</v>
+      </c>
+      <c r="F56" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="I56" s="139"/>
-      <c r="J56" s="139"/>
+      <c r="I56" s="135"/>
+      <c r="J56" s="135"/>
     </row>
     <row r="57" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="154"/>
+      <c r="A57" s="155"/>
       <c r="B57" s="44">
         <v>46322</v>
       </c>
       <c r="C57" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57" s="141" t="s">
+      <c r="D57" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="135" t="s">
         <v>27</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G57" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H57" s="139" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="H57" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="I57" s="141" t="s">
+      <c r="I57" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="J57" s="139"/>
+      <c r="J57" s="135"/>
     </row>
     <row r="58" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="154"/>
+      <c r="A58" s="155"/>
       <c r="B58" s="44">
         <v>46323</v>
       </c>
       <c r="C58" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="139" t="s">
+      <c r="D58" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="E58" s="139" t="s">
+      <c r="E58" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="F58" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G58" s="144"/>
-      <c r="H58" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I58" s="141" t="s">
+      <c r="F58" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="G58" s="138"/>
+      <c r="H58" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="J58" s="139"/>
+      <c r="J58" s="135"/>
     </row>
     <row r="59" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="154"/>
+      <c r="A59" s="155"/>
       <c r="B59" s="44">
         <v>46324</v>
       </c>
       <c r="C59" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E59" s="139"/>
+      <c r="D59" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" s="135"/>
       <c r="F59" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G59" s="139" t="s">
-        <v>245</v>
-      </c>
-      <c r="H59" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I59" s="139" t="s">
+        <v>240</v>
+      </c>
+      <c r="G59" s="135" t="s">
+        <v>244</v>
+      </c>
+      <c r="H59" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="J59" s="139"/>
+      <c r="J59" s="135"/>
     </row>
     <row r="60" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="154"/>
+      <c r="A60" s="155"/>
       <c r="B60" s="44">
         <v>46325</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60" s="139" t="s">
+      <c r="D60" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="F60" s="139" t="s">
+      <c r="F60" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="G60" s="139" t="s">
+      <c r="G60" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="H60" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I60" s="139"/>
+      <c r="H60" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" s="135"/>
       <c r="J60" s="81"/>
     </row>
     <row r="61" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="154"/>
+      <c r="A61" s="155"/>
       <c r="B61" s="44">
         <v>46326</v>
       </c>
       <c r="C61" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="139" t="s">
+      <c r="D61" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="F61" s="139"/>
-      <c r="G61" s="146"/>
-      <c r="H61" s="146"/>
-      <c r="I61" s="146"/>
-      <c r="J61" s="139"/>
+      <c r="F61" s="135"/>
+      <c r="G61" s="140"/>
+      <c r="H61" s="140"/>
+      <c r="I61" s="140"/>
+      <c r="J61" s="135"/>
     </row>
     <row r="62" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
@@ -6390,16 +6373,16 @@
       <c r="C62" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="142"/>
-      <c r="E62" s="142"/>
-      <c r="F62" s="142"/>
-      <c r="G62" s="142"/>
-      <c r="H62" s="142"/>
-      <c r="I62" s="142"/>
-      <c r="J62" s="142"/>
+      <c r="D62" s="136"/>
+      <c r="E62" s="136"/>
+      <c r="F62" s="136"/>
+      <c r="G62" s="136"/>
+      <c r="H62" s="136"/>
+      <c r="I62" s="136"/>
+      <c r="J62" s="136"/>
     </row>
     <row r="63" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="154" t="s">
+      <c r="A63" s="155" t="s">
         <v>31</v>
       </c>
       <c r="B63" s="44">
@@ -6408,157 +6391,157 @@
       <c r="C63" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="E63" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="139" t="s">
+      <c r="D63" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="E63" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G63" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H63" s="139" t="s">
+      <c r="G63" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="H63" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="I63" s="139" t="s">
+      <c r="I63" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="J63" s="139"/>
+      <c r="J63" s="135"/>
     </row>
     <row r="64" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="154"/>
+      <c r="A64" s="155"/>
       <c r="B64" s="44">
         <v>46329</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="141" t="s">
+      <c r="D64" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="F64" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="G64" s="143" t="s">
-        <v>211</v>
-      </c>
-      <c r="H64" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="I64" s="141" t="s">
-        <v>209</v>
-      </c>
-      <c r="J64" s="139"/>
+      <c r="F64" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="G64" s="137" t="s">
+        <v>210</v>
+      </c>
+      <c r="H64" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="J64" s="135"/>
     </row>
     <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="154"/>
+      <c r="A65" s="155"/>
       <c r="B65" s="44">
         <v>46330</v>
       </c>
       <c r="C65" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="139" t="s">
+      <c r="D65" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E65" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G65" s="139" t="s">
+      <c r="E65" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="H65" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="I65" s="139" t="s">
+      <c r="H65" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="I65" s="135" t="s">
         <v>27</v>
       </c>
       <c r="J65" s="81"/>
     </row>
     <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="154"/>
+      <c r="A66" s="155"/>
       <c r="B66" s="44">
         <v>46331</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D66" s="139" t="s">
+      <c r="D66" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F66" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G66" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H66" s="139" t="s">
+      <c r="E66" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="F66" s="145" t="s">
+        <v>240</v>
+      </c>
+      <c r="G66" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="I66" s="139"/>
-      <c r="J66" s="139"/>
+      <c r="I66" s="135"/>
+      <c r="J66" s="135"/>
     </row>
     <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="154"/>
+      <c r="A67" s="155"/>
       <c r="B67" s="44">
         <v>46332</v>
       </c>
       <c r="C67" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="141" t="s">
-        <v>209</v>
-      </c>
-      <c r="E67" s="141" t="s">
-        <v>209</v>
-      </c>
-      <c r="F67" s="139" t="s">
+      <c r="D67" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="E67" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="F67" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G67" s="141" t="s">
+      <c r="G67" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H67" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I67" s="139" t="s">
+      <c r="H67" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="J67" s="146"/>
+      <c r="J67" s="140"/>
     </row>
     <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="154"/>
+      <c r="A68" s="155"/>
       <c r="B68" s="44">
         <v>46333</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="F68" s="141" t="s">
-        <v>209</v>
-      </c>
-      <c r="G68" s="141"/>
-      <c r="H68" s="139"/>
-      <c r="I68" s="148"/>
-      <c r="J68" s="148"/>
+      <c r="D68" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="135" t="s">
+        <v>242</v>
+      </c>
+      <c r="F68" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="G68" s="135"/>
+      <c r="H68" s="135"/>
+      <c r="I68" s="142"/>
+      <c r="J68" s="142"/>
     </row>
     <row r="69" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
@@ -6568,7 +6551,7 @@
       <c r="C69" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="166" t="s">
+      <c r="D69" s="167" t="s">
         <v>29</v>
       </c>
       <c r="E69" s="167"/>
@@ -6576,10 +6559,10 @@
       <c r="G69" s="167"/>
       <c r="H69" s="167"/>
       <c r="I69" s="167"/>
-      <c r="J69" s="168"/>
+      <c r="J69" s="167"/>
     </row>
     <row r="70" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="154" t="s">
+      <c r="A70" s="155" t="s">
         <v>33</v>
       </c>
       <c r="B70" s="44">
@@ -6588,151 +6571,146 @@
       <c r="C70" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="E70" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70" s="139" t="s">
+      <c r="D70" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G70" s="139"/>
-      <c r="H70" s="139"/>
-      <c r="I70" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J70" s="139" t="s">
+      <c r="G70" s="135"/>
+      <c r="H70" s="135"/>
+      <c r="I70" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="154"/>
+      <c r="A71" s="155"/>
       <c r="B71" s="44">
         <v>46336</v>
       </c>
       <c r="C71" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71" s="133" t="s">
-        <v>240</v>
-      </c>
-      <c r="F71" s="139" t="s">
+      <c r="D71" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="G71" s="139"/>
-      <c r="H71" s="139"/>
-      <c r="I71" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J71" s="139" t="s">
+      <c r="G71" s="135"/>
+      <c r="H71" s="135"/>
+      <c r="I71" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="154"/>
+      <c r="A72" s="155"/>
       <c r="B72" s="44">
         <v>46337</v>
       </c>
       <c r="C72" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="141" t="s">
+      <c r="D72" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="E72" s="139" t="s">
+      <c r="E72" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="F72" s="139" t="s">
+      <c r="F72" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G72" s="144"/>
-      <c r="H72" s="139"/>
-      <c r="I72" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J72" s="139" t="s">
+      <c r="G72" s="138"/>
+      <c r="H72" s="135"/>
+      <c r="I72" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="154"/>
+      <c r="A73" s="155"/>
       <c r="B73" s="44">
         <v>46338</v>
       </c>
       <c r="C73" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="139" t="s">
+      <c r="D73" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="E73" s="139" t="s">
+      <c r="E73" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="F73" s="139" t="s">
+      <c r="F73" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G73" s="141" t="s">
+      <c r="G73" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H73" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="I73" s="139" t="s">
-        <v>209</v>
+      <c r="H73" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="I73" s="135" t="s">
+        <v>208</v>
       </c>
       <c r="J73" s="81"/>
     </row>
     <row r="74" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="154"/>
+      <c r="A74" s="155"/>
       <c r="B74" s="44">
         <v>46339</v>
       </c>
       <c r="C74" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D74" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F74" s="139" t="s">
-        <v>206</v>
-      </c>
-      <c r="G74" s="141" t="s">
-        <v>209</v>
-      </c>
-      <c r="H74" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I74" s="139" t="s">
-        <v>204</v>
-      </c>
+      <c r="D74" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="135" t="s">
+        <v>205</v>
+      </c>
+      <c r="G74" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="H74" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="135"/>
       <c r="J74" s="81"/>
     </row>
     <row r="75" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="154"/>
+      <c r="A75" s="155"/>
       <c r="B75" s="44">
         <v>46340</v>
       </c>
       <c r="C75" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E75" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="F75" s="139" t="s">
-        <v>204</v>
-      </c>
-      <c r="G75" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="H75" s="139" t="s">
-        <v>244</v>
+      <c r="D75" s="81"/>
+      <c r="E75" s="135"/>
+      <c r="F75" s="135"/>
+      <c r="G75" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="135" t="s">
+        <v>243</v>
       </c>
       <c r="I75" s="81"/>
       <c r="J75" s="81"/>
@@ -6745,24 +6723,20 @@
       <c r="C76" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="E76" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="F76" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="G76" s="142" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="142"/>
-      <c r="I76" s="142"/>
-      <c r="J76" s="142"/>
+      <c r="D76" s="136"/>
+      <c r="E76" s="136"/>
+      <c r="F76" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G76" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="136"/>
+      <c r="I76" s="136"/>
+      <c r="J76" s="136"/>
     </row>
     <row r="77" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="154" t="s">
+      <c r="A77" s="155" t="s">
         <v>34</v>
       </c>
       <c r="B77" s="44">
@@ -6771,169 +6745,169 @@
       <c r="C77" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="139" t="s">
-        <v>210</v>
-      </c>
-      <c r="E77" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" s="141" t="s">
+      <c r="D77" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="E77" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="G77" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="H77" s="139" t="s">
-        <v>244</v>
-      </c>
-      <c r="I77" s="139" t="s">
+      <c r="G77" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="135" t="s">
+        <v>243</v>
+      </c>
+      <c r="I77" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="J77" s="139" t="s">
+      <c r="J77" s="135" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="154"/>
+      <c r="A78" s="155"/>
       <c r="B78" s="44">
         <v>46343</v>
       </c>
       <c r="C78" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D78" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F78" s="140" t="s">
-        <v>27</v>
-      </c>
-      <c r="G78" s="139" t="s">
+      <c r="D78" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="E78" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G78" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="H78" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I78" s="139" t="s">
+      <c r="H78" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="J78" s="139" t="s">
+      <c r="J78" s="135" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="154"/>
+      <c r="A79" s="155"/>
       <c r="B79" s="44">
         <v>46344</v>
       </c>
       <c r="C79" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D79" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="F79" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G79" s="144"/>
-      <c r="H79" s="139" t="s">
+      <c r="D79" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="F79" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" s="138"/>
+      <c r="H79" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="I79" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J79" s="139" t="s">
+      <c r="I79" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="J79" s="135" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="154"/>
+      <c r="A80" s="155"/>
       <c r="B80" s="44">
         <v>46345</v>
       </c>
       <c r="C80" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D80" s="139" t="s">
+      <c r="D80" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="E80" s="139" t="s">
+      <c r="E80" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="F80" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G80" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="H80" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="I80" s="143" t="s">
-        <v>248</v>
-      </c>
-      <c r="J80" s="140" t="s">
-        <v>209</v>
+      <c r="F80" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="H80" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" s="137" t="s">
+        <v>247</v>
+      </c>
+      <c r="J80" s="137" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="154"/>
+      <c r="A81" s="155"/>
       <c r="B81" s="44">
         <v>46346</v>
       </c>
       <c r="C81" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" s="139" t="s">
+      <c r="D81" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="F81" s="139" t="s">
+      <c r="F81" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G81" s="141" t="s">
+      <c r="G81" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H81" s="139" t="s">
+      <c r="H81" s="135" t="s">
+        <v>207</v>
+      </c>
+      <c r="I81" s="135" t="s">
         <v>208</v>
       </c>
-      <c r="I81" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="J81" s="139"/>
+      <c r="J81" s="135"/>
     </row>
     <row r="82" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="154"/>
+      <c r="A82" s="155"/>
       <c r="B82" s="44">
         <v>46347</v>
       </c>
       <c r="C82" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" s="143" t="s">
-        <v>211</v>
-      </c>
-      <c r="F82" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G82" s="139" t="s">
+      <c r="D82" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="137" t="s">
+        <v>210</v>
+      </c>
+      <c r="F82" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="H82" s="139" t="s">
+      <c r="H82" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="I82" s="139"/>
-      <c r="J82" s="148"/>
+      <c r="I82" s="135"/>
+      <c r="J82" s="142"/>
     </row>
     <row r="83" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
@@ -6943,16 +6917,16 @@
       <c r="C83" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D83" s="142"/>
-      <c r="E83" s="142"/>
-      <c r="F83" s="142"/>
-      <c r="G83" s="142"/>
-      <c r="H83" s="142"/>
-      <c r="I83" s="142"/>
-      <c r="J83" s="142"/>
+      <c r="D83" s="136"/>
+      <c r="E83" s="136"/>
+      <c r="F83" s="136"/>
+      <c r="G83" s="136"/>
+      <c r="H83" s="136"/>
+      <c r="I83" s="136"/>
+      <c r="J83" s="136"/>
     </row>
     <row r="84" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="154" t="s">
+      <c r="A84" s="155" t="s">
         <v>35</v>
       </c>
       <c r="B84" s="44">
@@ -6961,7 +6935,7 @@
       <c r="C84" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="166" t="s">
+      <c r="D84" s="167" t="s">
         <v>152</v>
       </c>
       <c r="E84" s="167"/>
@@ -6969,17 +6943,17 @@
       <c r="G84" s="167"/>
       <c r="H84" s="167"/>
       <c r="I84" s="167"/>
-      <c r="J84" s="168"/>
+      <c r="J84" s="167"/>
     </row>
     <row r="85" spans="1:10" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="154"/>
+      <c r="A85" s="155"/>
       <c r="B85" s="44">
         <v>46350</v>
       </c>
       <c r="C85" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D85" s="166" t="s">
+      <c r="D85" s="167" t="s">
         <v>32</v>
       </c>
       <c r="E85" s="167"/>
@@ -6987,87 +6961,88 @@
       <c r="G85" s="167"/>
       <c r="H85" s="167"/>
       <c r="I85" s="167"/>
-      <c r="J85" s="168"/>
+      <c r="J85" s="167"/>
     </row>
     <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="154"/>
+      <c r="A86" s="155"/>
       <c r="B86" s="44">
         <v>46351</v>
       </c>
       <c r="C86" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D86" s="139" t="s">
-        <v>212</v>
-      </c>
-      <c r="E86" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F86" s="139" t="s">
+      <c r="D86" s="135" t="s">
+        <v>211</v>
+      </c>
+      <c r="E86" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="135" t="s">
         <v>193</v>
       </c>
-      <c r="G86" s="144"/>
-      <c r="H86" s="139" t="s">
+      <c r="G86" s="138"/>
+      <c r="H86" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="J86" s="139"/>
+      <c r="I86" s="81"/>
+      <c r="J86" s="135"/>
     </row>
     <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="154"/>
+      <c r="A87" s="155"/>
       <c r="B87" s="44">
         <v>46352</v>
       </c>
       <c r="C87" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="139" t="s">
+      <c r="D87" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="E87" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F87" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="G87" s="139" t="s">
+      <c r="E87" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F87" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="H87" s="139" t="s">
+      <c r="H87" s="135" t="s">
         <v>194</v>
       </c>
-      <c r="I87" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="J87" s="146"/>
+      <c r="I87" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J87" s="140"/>
     </row>
     <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="154"/>
+      <c r="A88" s="155"/>
       <c r="B88" s="44">
         <v>46353</v>
       </c>
       <c r="C88" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="E88" s="139" t="s">
+      <c r="D88" s="135" t="s">
+        <v>251</v>
+      </c>
+      <c r="E88" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="F88" s="139" t="s">
+      <c r="F88" s="135" t="s">
         <v>202</v>
       </c>
-      <c r="G88" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" s="143" t="s">
-        <v>27</v>
-      </c>
-      <c r="I88" s="139"/>
-      <c r="J88" s="139"/>
+      <c r="G88" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="135"/>
+      <c r="J88" s="135"/>
     </row>
     <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="154"/>
+      <c r="A89" s="155"/>
       <c r="B89" s="44">
         <v>46354</v>
       </c>
@@ -7077,10 +7052,10 @@
       <c r="D89" s="81"/>
       <c r="E89" s="81"/>
       <c r="F89" s="81"/>
-      <c r="G89" s="148"/>
-      <c r="H89" s="148"/>
-      <c r="I89" s="139"/>
-      <c r="J89" s="139"/>
+      <c r="G89" s="142"/>
+      <c r="H89" s="142"/>
+      <c r="I89" s="135"/>
+      <c r="J89" s="135"/>
     </row>
     <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
@@ -7090,16 +7065,16 @@
       <c r="C90" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D90" s="142"/>
-      <c r="E90" s="142"/>
-      <c r="F90" s="142"/>
-      <c r="G90" s="142"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="142"/>
-      <c r="J90" s="142"/>
+      <c r="D90" s="136"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="136"/>
+      <c r="H90" s="136"/>
+      <c r="I90" s="136"/>
+      <c r="J90" s="136"/>
     </row>
     <row r="91" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="154" t="s">
+      <c r="A91" s="155" t="s">
         <v>36</v>
       </c>
       <c r="B91" s="44">
@@ -7108,95 +7083,95 @@
       <c r="C91" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="156" t="s">
-        <v>249</v>
-      </c>
-      <c r="E91" s="156"/>
-      <c r="F91" s="156"/>
-      <c r="G91" s="156"/>
-      <c r="H91" s="156"/>
-      <c r="I91" s="156"/>
-      <c r="J91" s="157"/>
+      <c r="D91" s="157" t="s">
+        <v>248</v>
+      </c>
+      <c r="E91" s="157"/>
+      <c r="F91" s="157"/>
+      <c r="G91" s="157"/>
+      <c r="H91" s="157"/>
+      <c r="I91" s="157"/>
+      <c r="J91" s="158"/>
     </row>
     <row r="92" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="154"/>
+      <c r="A92" s="155"/>
       <c r="B92" s="44">
         <v>46357</v>
       </c>
       <c r="C92" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D92" s="158"/>
-      <c r="E92" s="158"/>
-      <c r="F92" s="158"/>
-      <c r="G92" s="158"/>
-      <c r="H92" s="158"/>
-      <c r="I92" s="158"/>
-      <c r="J92" s="159"/>
+      <c r="D92" s="159"/>
+      <c r="E92" s="159"/>
+      <c r="F92" s="159"/>
+      <c r="G92" s="159"/>
+      <c r="H92" s="159"/>
+      <c r="I92" s="159"/>
+      <c r="J92" s="160"/>
     </row>
     <row r="93" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="154"/>
+      <c r="A93" s="155"/>
       <c r="B93" s="44">
         <v>46358</v>
       </c>
       <c r="C93" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D93" s="158"/>
-      <c r="E93" s="158"/>
-      <c r="F93" s="158"/>
-      <c r="G93" s="158"/>
-      <c r="H93" s="158"/>
-      <c r="I93" s="158"/>
-      <c r="J93" s="159"/>
+      <c r="D93" s="159"/>
+      <c r="E93" s="159"/>
+      <c r="F93" s="159"/>
+      <c r="G93" s="159"/>
+      <c r="H93" s="159"/>
+      <c r="I93" s="159"/>
+      <c r="J93" s="160"/>
     </row>
     <row r="94" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="154"/>
+      <c r="A94" s="155"/>
       <c r="B94" s="44">
         <v>46359</v>
       </c>
       <c r="C94" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D94" s="158"/>
-      <c r="E94" s="158"/>
-      <c r="F94" s="158"/>
-      <c r="G94" s="158"/>
-      <c r="H94" s="158"/>
-      <c r="I94" s="158"/>
-      <c r="J94" s="159"/>
+      <c r="D94" s="159"/>
+      <c r="E94" s="159"/>
+      <c r="F94" s="159"/>
+      <c r="G94" s="159"/>
+      <c r="H94" s="159"/>
+      <c r="I94" s="159"/>
+      <c r="J94" s="160"/>
     </row>
     <row r="95" spans="1:10" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="154"/>
+      <c r="A95" s="155"/>
       <c r="B95" s="44">
         <v>46360</v>
       </c>
       <c r="C95" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D95" s="158"/>
-      <c r="E95" s="158"/>
-      <c r="F95" s="158"/>
-      <c r="G95" s="158"/>
-      <c r="H95" s="158"/>
-      <c r="I95" s="158"/>
-      <c r="J95" s="159"/>
+      <c r="D95" s="159"/>
+      <c r="E95" s="159"/>
+      <c r="F95" s="159"/>
+      <c r="G95" s="159"/>
+      <c r="H95" s="159"/>
+      <c r="I95" s="159"/>
+      <c r="J95" s="160"/>
     </row>
     <row r="96" spans="1:10" s="4" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="155"/>
+      <c r="A96" s="156"/>
       <c r="B96" s="44">
         <v>46361</v>
       </c>
       <c r="C96" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="160"/>
-      <c r="E96" s="160"/>
-      <c r="F96" s="160"/>
-      <c r="G96" s="160"/>
-      <c r="H96" s="160"/>
-      <c r="I96" s="160"/>
-      <c r="J96" s="161"/>
+      <c r="D96" s="161"/>
+      <c r="E96" s="161"/>
+      <c r="F96" s="161"/>
+      <c r="G96" s="161"/>
+      <c r="H96" s="161"/>
+      <c r="I96" s="161"/>
+      <c r="J96" s="162"/>
     </row>
     <row r="97" spans="1:10" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A97" s="16"/>
@@ -7211,20 +7186,20 @@
       <c r="J97" s="19"/>
     </row>
     <row r="99" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A99" s="162" t="s">
+      <c r="A99" s="163" t="s">
+        <v>223</v>
+      </c>
+      <c r="B99" s="163"/>
+      <c r="C99" s="163"/>
+      <c r="D99" s="163"/>
+      <c r="E99" s="131" t="s">
         <v>224</v>
       </c>
-      <c r="B99" s="162"/>
-      <c r="C99" s="162"/>
-      <c r="D99" s="162"/>
-      <c r="E99" s="131" t="s">
+      <c r="F99" s="131" t="s">
         <v>225</v>
       </c>
-      <c r="F99" s="131" t="s">
+      <c r="G99" s="131" t="s">
         <v>226</v>
-      </c>
-      <c r="G99" s="131" t="s">
-        <v>227</v>
       </c>
       <c r="H99" s="131" t="s">
         <v>41</v>
@@ -7233,67 +7208,67 @@
       <c r="J99" s="114"/>
     </row>
     <row r="100" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="163" t="s">
+      <c r="A100" s="164" t="s">
+        <v>227</v>
+      </c>
+      <c r="B100" s="164"/>
+      <c r="C100" s="164"/>
+      <c r="D100" s="164"/>
+      <c r="E100" s="132" t="s">
         <v>228</v>
       </c>
-      <c r="B100" s="163"/>
-      <c r="C100" s="163"/>
-      <c r="D100" s="163"/>
-      <c r="E100" s="132" t="s">
+      <c r="F100" s="132" t="s">
         <v>229</v>
       </c>
-      <c r="F100" s="132" t="s">
+      <c r="G100" s="132" t="s">
         <v>230</v>
       </c>
-      <c r="G100" s="132" t="s">
+      <c r="H100" s="132" t="s">
         <v>231</v>
-      </c>
-      <c r="H100" s="132" t="s">
-        <v>232</v>
       </c>
       <c r="I100" s="114"/>
       <c r="J100" s="114"/>
     </row>
     <row r="101" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="163" t="s">
+      <c r="A101" s="164" t="s">
+        <v>232</v>
+      </c>
+      <c r="B101" s="164"/>
+      <c r="C101" s="164"/>
+      <c r="D101" s="164"/>
+      <c r="E101" s="132" t="s">
         <v>233</v>
       </c>
-      <c r="B101" s="163"/>
-      <c r="C101" s="163"/>
-      <c r="D101" s="163"/>
-      <c r="E101" s="132" t="s">
+      <c r="F101" s="132" t="s">
         <v>234</v>
       </c>
-      <c r="F101" s="132" t="s">
-        <v>235</v>
-      </c>
       <c r="G101" s="132" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H101" s="132" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I101" s="114"/>
       <c r="J101" s="114"/>
     </row>
     <row r="102" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="163" t="s">
+      <c r="A102" s="164" t="s">
+        <v>235</v>
+      </c>
+      <c r="B102" s="164"/>
+      <c r="C102" s="164"/>
+      <c r="D102" s="164"/>
+      <c r="E102" s="132" t="s">
         <v>236</v>
       </c>
-      <c r="B102" s="163"/>
-      <c r="C102" s="163"/>
-      <c r="D102" s="163"/>
-      <c r="E102" s="132" t="s">
+      <c r="F102" s="132" t="s">
         <v>237</v>
       </c>
-      <c r="F102" s="132" t="s">
+      <c r="G102" s="132" t="s">
+        <v>230</v>
+      </c>
+      <c r="H102" s="132" t="s">
         <v>238</v>
-      </c>
-      <c r="G102" s="132" t="s">
-        <v>231</v>
-      </c>
-      <c r="H102" s="132" t="s">
-        <v>239</v>
       </c>
       <c r="I102" s="114"/>
       <c r="J102" s="114"/>
@@ -7311,16 +7286,16 @@
       <c r="J103" s="114"/>
     </row>
     <row r="104" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="164" t="s">
-        <v>223</v>
-      </c>
-      <c r="B104" s="165"/>
-      <c r="C104" s="165"/>
-      <c r="D104" s="165"/>
-      <c r="E104" s="165"/>
-      <c r="F104" s="165"/>
-      <c r="G104" s="165"/>
-      <c r="H104" s="165"/>
+      <c r="A104" s="165" t="s">
+        <v>222</v>
+      </c>
+      <c r="B104" s="166"/>
+      <c r="C104" s="166"/>
+      <c r="D104" s="166"/>
+      <c r="E104" s="166"/>
+      <c r="F104" s="166"/>
+      <c r="G104" s="166"/>
+      <c r="H104" s="166"/>
       <c r="I104" s="129"/>
       <c r="J104" s="130"/>
     </row>
@@ -7328,11 +7303,11 @@
       <c r="A105" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="153" t="s">
+      <c r="B105" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="C105" s="153"/>
-      <c r="D105" s="153"/>
+      <c r="C105" s="154"/>
+      <c r="D105" s="154"/>
       <c r="E105" s="116" t="s">
         <v>41</v>
       </c>
@@ -7352,14 +7327,14 @@
       <c r="A106" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="B106" s="235" t="s">
-        <v>214</v>
-      </c>
-      <c r="C106" s="235" t="s">
-        <v>214</v>
-      </c>
-      <c r="D106" s="235" t="s">
-        <v>214</v>
+      <c r="B106" s="153" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="153" t="s">
+        <v>213</v>
+      </c>
+      <c r="D106" s="153" t="s">
+        <v>213</v>
       </c>
       <c r="E106" s="123" t="s">
         <v>56</v>
@@ -7380,14 +7355,14 @@
       <c r="A107" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="B107" s="235" t="s">
-        <v>215</v>
-      </c>
-      <c r="C107" s="235" t="s">
-        <v>215</v>
-      </c>
-      <c r="D107" s="235" t="s">
-        <v>215</v>
+      <c r="B107" s="153" t="s">
+        <v>214</v>
+      </c>
+      <c r="C107" s="153" t="s">
+        <v>214</v>
+      </c>
+      <c r="D107" s="153" t="s">
+        <v>214</v>
       </c>
       <c r="E107" s="123" t="s">
         <v>60</v>
@@ -7408,14 +7383,14 @@
       <c r="A108" s="122" t="s">
         <v>74</v>
       </c>
-      <c r="B108" s="235" t="s">
-        <v>216</v>
-      </c>
-      <c r="C108" s="235" t="s">
-        <v>216</v>
-      </c>
-      <c r="D108" s="235" t="s">
-        <v>216</v>
+      <c r="B108" s="153" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" s="153" t="s">
+        <v>215</v>
+      </c>
+      <c r="D108" s="153" t="s">
+        <v>215</v>
       </c>
       <c r="E108" s="123" t="s">
         <v>76</v>
@@ -7436,14 +7411,14 @@
       <c r="A109" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="B109" s="235" t="s">
-        <v>217</v>
-      </c>
-      <c r="C109" s="235" t="s">
-        <v>217</v>
-      </c>
-      <c r="D109" s="235" t="s">
-        <v>217</v>
+      <c r="B109" s="153" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="153" t="s">
+        <v>216</v>
+      </c>
+      <c r="D109" s="153" t="s">
+        <v>216</v>
       </c>
       <c r="E109" s="123" t="s">
         <v>79</v>
@@ -7464,14 +7439,14 @@
       <c r="A110" s="122" t="s">
         <v>157</v>
       </c>
-      <c r="B110" s="235" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" s="235" t="s">
-        <v>218</v>
-      </c>
-      <c r="D110" s="235" t="s">
-        <v>218</v>
+      <c r="B110" s="153" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="153" t="s">
+        <v>217</v>
+      </c>
+      <c r="D110" s="153" t="s">
+        <v>217</v>
       </c>
       <c r="E110" s="123" t="s">
         <v>85</v>
@@ -7493,13 +7468,13 @@
         <v>86</v>
       </c>
       <c r="B111" s="152" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C111" s="152" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D111" s="152" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E111" s="123" t="s">
         <v>192</v>
@@ -7520,14 +7495,14 @@
       <c r="A112" s="122" t="s">
         <v>159</v>
       </c>
-      <c r="B112" s="235" t="s">
-        <v>220</v>
-      </c>
-      <c r="C112" s="235" t="s">
-        <v>220</v>
-      </c>
-      <c r="D112" s="235" t="s">
-        <v>220</v>
+      <c r="B112" s="153" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" s="153" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" s="153" t="s">
+        <v>219</v>
       </c>
       <c r="E112" s="123" t="s">
         <v>82</v>
@@ -7549,13 +7524,13 @@
         <v>64</v>
       </c>
       <c r="B113" s="152" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C113" s="152" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D113" s="152" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E113" s="123" t="s">
         <v>187</v>
@@ -7574,19 +7549,19 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="122" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B114" s="152" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C114" s="152" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D114" s="152" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E114" s="123" t="s">
-        <v>191</v>
+        <v>94</v>
       </c>
       <c r="F114" s="119">
         <v>4</v>
@@ -7595,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="120">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I114" s="125"/>
       <c r="J114" s="126"/>
@@ -7671,44 +7646,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
     </row>
     <row r="4" spans="1:7" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="203" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="203"/>
-      <c r="C4" s="203"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="202"/>
       <c r="D4" s="88" t="s">
         <v>111</v>
       </c>
@@ -7723,7 +7698,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="205"/>
+      <c r="A5" s="204"/>
       <c r="B5" s="89">
         <v>46356</v>
       </c>
@@ -7736,7 +7711,7 @@
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="205"/>
+      <c r="A6" s="204"/>
       <c r="B6" s="89">
         <v>46357</v>
       </c>
@@ -7749,7 +7724,7 @@
       <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="205"/>
+      <c r="A7" s="204"/>
       <c r="B7" s="89">
         <v>46358</v>
       </c>
@@ -7762,7 +7737,7 @@
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="205"/>
+      <c r="A8" s="204"/>
       <c r="B8" s="89">
         <v>46359</v>
       </c>
@@ -7775,7 +7750,7 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="205"/>
+      <c r="A9" s="204"/>
       <c r="B9" s="89">
         <v>46360</v>
       </c>
@@ -7788,7 +7763,7 @@
       <c r="G9" s="81"/>
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="206"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="89">
         <v>46361</v>
       </c>
@@ -7810,140 +7785,140 @@
       <c r="A12" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="201" t="s">
+      <c r="B12" s="200" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
+      <c r="C12" s="200"/>
+      <c r="D12" s="201"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:7" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
-      <c r="B13" s="210"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="212"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="211"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:7" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26"/>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="214"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="213"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
-      <c r="B15" s="215"/>
-      <c r="C15" s="215"/>
-      <c r="D15" s="216"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="215"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
-      <c r="B16" s="215"/>
-      <c r="C16" s="215"/>
-      <c r="D16" s="216"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="215"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
-      <c r="B17" s="215"/>
-      <c r="C17" s="215"/>
-      <c r="D17" s="216"/>
+      <c r="B17" s="214"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="215"/>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
-      <c r="B18" s="215"/>
-      <c r="C18" s="215"/>
-      <c r="D18" s="216"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="214"/>
+      <c r="D18" s="215"/>
     </row>
     <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
-      <c r="B19" s="207"/>
-      <c r="C19" s="208"/>
-      <c r="D19" s="209"/>
+      <c r="B19" s="206"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="208"/>
     </row>
     <row r="20" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26"/>
-      <c r="B20" s="207"/>
-      <c r="C20" s="208"/>
-      <c r="D20" s="209"/>
+      <c r="B20" s="206"/>
+      <c r="C20" s="207"/>
+      <c r="D20" s="208"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26"/>
-      <c r="B21" s="207"/>
-      <c r="C21" s="208"/>
-      <c r="D21" s="209"/>
+      <c r="B21" s="206"/>
+      <c r="C21" s="207"/>
+      <c r="D21" s="208"/>
     </row>
     <row r="22" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26"/>
-      <c r="B22" s="207"/>
-      <c r="C22" s="208"/>
-      <c r="D22" s="209"/>
+      <c r="B22" s="206"/>
+      <c r="C22" s="207"/>
+      <c r="D22" s="208"/>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
-      <c r="B23" s="207"/>
-      <c r="C23" s="208"/>
-      <c r="D23" s="209"/>
+      <c r="B23" s="206"/>
+      <c r="C23" s="207"/>
+      <c r="D23" s="208"/>
     </row>
     <row r="24" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
-      <c r="B24" s="207"/>
-      <c r="C24" s="208"/>
-      <c r="D24" s="209"/>
+      <c r="B24" s="206"/>
+      <c r="C24" s="207"/>
+      <c r="D24" s="208"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
-      <c r="B25" s="207"/>
-      <c r="C25" s="208"/>
-      <c r="D25" s="209"/>
+      <c r="B25" s="206"/>
+      <c r="C25" s="207"/>
+      <c r="D25" s="208"/>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26"/>
-      <c r="B26" s="207"/>
-      <c r="C26" s="208"/>
-      <c r="D26" s="209"/>
+      <c r="B26" s="206"/>
+      <c r="C26" s="207"/>
+      <c r="D26" s="208"/>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
-      <c r="B27" s="207"/>
-      <c r="C27" s="208"/>
-      <c r="D27" s="209"/>
+      <c r="B27" s="206"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="208"/>
       <c r="F27" s="34"/>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
-      <c r="B28" s="207"/>
-      <c r="C28" s="208"/>
-      <c r="D28" s="209"/>
+      <c r="B28" s="206"/>
+      <c r="C28" s="207"/>
+      <c r="D28" s="208"/>
       <c r="F28" s="35"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26"/>
-      <c r="B29" s="207"/>
-      <c r="C29" s="208"/>
-      <c r="D29" s="209"/>
+      <c r="B29" s="206"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="208"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26"/>
-      <c r="B30" s="215"/>
-      <c r="C30" s="215"/>
-      <c r="D30" s="216"/>
+      <c r="B30" s="214"/>
+      <c r="C30" s="214"/>
+      <c r="D30" s="215"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26"/>
-      <c r="B31" s="215"/>
-      <c r="C31" s="215"/>
-      <c r="D31" s="216"/>
+      <c r="B31" s="214"/>
+      <c r="C31" s="214"/>
+      <c r="D31" s="215"/>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="28"/>
-      <c r="B32" s="217" t="s">
+      <c r="B32" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="217"/>
-      <c r="D32" s="218"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="217"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8007,44 +7982,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
     </row>
     <row r="4" spans="1:7" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="218" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="222"/>
-      <c r="C4" s="222"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
       <c r="D4" s="39" t="s">
         <v>111</v>
       </c>
@@ -8059,7 +8034,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="220"/>
+      <c r="A5" s="219"/>
       <c r="B5" s="37"/>
       <c r="C5" s="38"/>
       <c r="D5" s="10"/>
@@ -8068,7 +8043,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="220"/>
+      <c r="A6" s="219"/>
       <c r="B6" s="37"/>
       <c r="C6" s="38"/>
       <c r="D6" s="10"/>
@@ -8077,7 +8052,7 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="220"/>
+      <c r="A7" s="219"/>
       <c r="B7" s="37"/>
       <c r="C7" s="38"/>
       <c r="D7" s="10"/>
@@ -8086,7 +8061,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="220"/>
+      <c r="A8" s="219"/>
       <c r="B8" s="37"/>
       <c r="C8" s="38"/>
       <c r="D8" s="10"/>
@@ -8095,7 +8070,7 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="221"/>
+      <c r="A9" s="220"/>
       <c r="B9" s="41"/>
       <c r="C9" s="42"/>
       <c r="D9" s="36"/>
@@ -8140,16 +8115,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="230" t="s">
+      <c r="B1" s="229" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -8162,10 +8137,10 @@
       <c r="D2" s="53"/>
       <c r="E2" s="53"/>
       <c r="F2" s="53"/>
-      <c r="G2" s="225" t="s">
+      <c r="G2" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="225"/>
+      <c r="H2" s="224"/>
     </row>
     <row r="3" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="46" t="s">
@@ -8204,10 +8179,10 @@
       <c r="D5" s="53"/>
       <c r="E5" s="53"/>
       <c r="F5" s="53"/>
-      <c r="G5" s="225" t="s">
+      <c r="G5" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="225"/>
+      <c r="H5" s="224"/>
     </row>
     <row r="6" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="46" t="s">
@@ -8252,10 +8227,10 @@
       <c r="D8" s="53"/>
       <c r="E8" s="53"/>
       <c r="F8" s="53"/>
-      <c r="G8" s="225" t="s">
+      <c r="G8" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="225"/>
+      <c r="H8" s="224"/>
     </row>
     <row r="9" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="46" t="s">
@@ -8294,10 +8269,10 @@
       <c r="D11" s="53"/>
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
-      <c r="G11" s="225" t="s">
+      <c r="G11" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H11" s="225"/>
+      <c r="H11" s="224"/>
     </row>
     <row r="12" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="46" t="s">
@@ -8336,10 +8311,10 @@
       <c r="D14" s="53"/>
       <c r="E14" s="53"/>
       <c r="F14" s="53"/>
-      <c r="G14" s="225" t="s">
+      <c r="G14" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H14" s="225"/>
+      <c r="H14" s="224"/>
     </row>
     <row r="15" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="46" t="s">
@@ -8378,10 +8353,10 @@
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
-      <c r="G17" s="225" t="s">
+      <c r="G17" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H17" s="225"/>
+      <c r="H17" s="224"/>
     </row>
     <row r="18" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="46" t="s">
@@ -8421,10 +8396,10 @@
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
-      <c r="H20" s="225" t="s">
+      <c r="H20" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="225"/>
+      <c r="I20" s="224"/>
     </row>
     <row r="21" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="46" t="s">
@@ -8463,10 +8438,10 @@
       <c r="D23" s="53"/>
       <c r="E23" s="53"/>
       <c r="F23" s="53"/>
-      <c r="G23" s="225" t="s">
+      <c r="G23" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H23" s="225"/>
+      <c r="H23" s="224"/>
     </row>
     <row r="24" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="46" t="s">
@@ -8505,10 +8480,10 @@
       <c r="D26" s="53"/>
       <c r="E26" s="53"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="225" t="s">
+      <c r="G26" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H26" s="225"/>
+      <c r="H26" s="224"/>
     </row>
     <row r="27" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="46" t="s">
@@ -8547,10 +8522,10 @@
       <c r="D29" s="53"/>
       <c r="E29" s="53"/>
       <c r="F29" s="53"/>
-      <c r="G29" s="225" t="s">
+      <c r="G29" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H29" s="225"/>
+      <c r="H29" s="224"/>
     </row>
     <row r="30" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="46" t="s">
@@ -8589,10 +8564,10 @@
       <c r="D32" s="53"/>
       <c r="E32" s="53"/>
       <c r="F32" s="53"/>
-      <c r="G32" s="225" t="s">
+      <c r="G32" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H32" s="225"/>
+      <c r="H32" s="224"/>
     </row>
     <row r="33" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="46" t="s">
@@ -8631,10 +8606,10 @@
       <c r="D35" s="53"/>
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
-      <c r="G35" s="225" t="s">
+      <c r="G35" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H35" s="225"/>
+      <c r="H35" s="224"/>
     </row>
     <row r="36" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="46" t="s">
@@ -8673,10 +8648,10 @@
       <c r="D38" s="53"/>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
-      <c r="G38" s="225" t="s">
+      <c r="G38" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H38" s="225"/>
+      <c r="H38" s="224"/>
     </row>
     <row r="39" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="46" t="s">
@@ -8715,10 +8690,10 @@
       <c r="D41" s="53"/>
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
-      <c r="G41" s="225" t="s">
+      <c r="G41" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="225"/>
+      <c r="H41" s="224"/>
     </row>
     <row r="42" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="52" t="s">
@@ -8757,10 +8732,10 @@
       <c r="D44" s="53"/>
       <c r="E44" s="53"/>
       <c r="F44" s="53"/>
-      <c r="G44" s="225" t="s">
+      <c r="G44" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H44" s="225"/>
+      <c r="H44" s="224"/>
     </row>
     <row r="45" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="46" t="s">
@@ -8799,10 +8774,10 @@
       <c r="D47" s="53"/>
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
-      <c r="G47" s="225" t="s">
+      <c r="G47" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H47" s="225"/>
+      <c r="H47" s="224"/>
     </row>
     <row r="48" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="46" t="s">
@@ -8841,10 +8816,10 @@
       <c r="D50" s="53"/>
       <c r="E50" s="53"/>
       <c r="F50" s="53"/>
-      <c r="G50" s="225" t="s">
+      <c r="G50" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H50" s="225"/>
+      <c r="H50" s="224"/>
     </row>
     <row r="51" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="46" t="s">
@@ -8883,10 +8858,10 @@
       <c r="D53" s="53"/>
       <c r="E53" s="53"/>
       <c r="F53" s="53"/>
-      <c r="G53" s="225" t="s">
+      <c r="G53" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H53" s="225"/>
+      <c r="H53" s="224"/>
     </row>
     <row r="54" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="46" t="s">
@@ -8925,46 +8900,46 @@
       <c r="D56" s="53"/>
       <c r="E56" s="53"/>
       <c r="F56" s="53"/>
-      <c r="G56" s="225" t="s">
+      <c r="G56" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H56" s="225"/>
+      <c r="H56" s="224"/>
     </row>
     <row r="57" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="226" t="s">
+      <c r="B57" s="225" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="223" t="s">
+      <c r="C57" s="222" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="226" t="s">
+      <c r="D57" s="225" t="s">
         <v>124</v>
       </c>
-      <c r="E57" s="223" t="s">
+      <c r="E57" s="222" t="s">
         <v>126</v>
       </c>
-      <c r="F57" s="226" t="s">
+      <c r="F57" s="225" t="s">
         <v>125</v>
       </c>
-      <c r="G57" s="223" t="s">
+      <c r="G57" s="222" t="s">
         <v>126</v>
       </c>
-      <c r="H57" s="228" t="s">
+      <c r="H57" s="227" t="s">
         <v>127</v>
       </c>
-      <c r="I57" s="223" t="s">
+      <c r="I57" s="222" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="227"/>
-      <c r="C58" s="224"/>
-      <c r="D58" s="227"/>
-      <c r="E58" s="224"/>
-      <c r="F58" s="227"/>
-      <c r="G58" s="224"/>
-      <c r="H58" s="229"/>
-      <c r="I58" s="224"/>
+      <c r="B58" s="226"/>
+      <c r="C58" s="223"/>
+      <c r="D58" s="226"/>
+      <c r="E58" s="223"/>
+      <c r="F58" s="226"/>
+      <c r="G58" s="223"/>
+      <c r="H58" s="228"/>
+      <c r="I58" s="223"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B60" s="54" t="s">
@@ -8982,10 +8957,10 @@
       <c r="D62" s="53"/>
       <c r="E62" s="53"/>
       <c r="F62" s="53"/>
-      <c r="G62" s="225" t="s">
+      <c r="G62" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H62" s="225"/>
+      <c r="H62" s="224"/>
     </row>
     <row r="63" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="46" t="s">
@@ -9021,10 +8996,10 @@
       <c r="D66" s="53"/>
       <c r="E66" s="53"/>
       <c r="F66" s="53"/>
-      <c r="G66" s="225" t="s">
+      <c r="G66" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H66" s="225"/>
+      <c r="H66" s="224"/>
     </row>
     <row r="67" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="46" t="s">
@@ -9060,10 +9035,10 @@
       <c r="D70" s="53"/>
       <c r="E70" s="53"/>
       <c r="F70" s="53"/>
-      <c r="G70" s="225" t="s">
+      <c r="G70" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H70" s="225"/>
+      <c r="H70" s="224"/>
     </row>
     <row r="71" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="46" t="s">
@@ -9148,44 +9123,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
     </row>
     <row r="4" spans="1:7" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="231" t="s">
+      <c r="A4" s="230" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="222"/>
-      <c r="C4" s="222"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
       <c r="D4" s="39" t="s">
         <v>111</v>
       </c>
@@ -9200,7 +9175,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="232"/>
+      <c r="A5" s="231"/>
       <c r="B5" s="37">
         <v>45992</v>
       </c>
@@ -9221,7 +9196,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="232"/>
+      <c r="A6" s="231"/>
       <c r="B6" s="37">
         <v>45993</v>
       </c>
@@ -9242,7 +9217,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="232"/>
+      <c r="A7" s="231"/>
       <c r="B7" s="37">
         <v>45994</v>
       </c>
@@ -9261,7 +9236,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="232"/>
+      <c r="A8" s="231"/>
       <c r="B8" s="37">
         <v>45995</v>
       </c>
@@ -9282,7 +9257,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="233"/>
+      <c r="A9" s="232"/>
       <c r="B9" s="41">
         <v>45996</v>
       </c>
@@ -9315,218 +9290,218 @@
       <c r="A11" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="201" t="s">
+      <c r="B11" s="200" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="201"/>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:7" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="210" t="s">
+      <c r="B12" s="209" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="211"/>
-      <c r="D12" s="212"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="211"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:7" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="213" t="s">
+      <c r="B13" s="212" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="213"/>
-      <c r="D13" s="214"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="213"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="215" t="s">
+      <c r="B14" s="214" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="215"/>
-      <c r="D14" s="216"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="215"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="215" t="s">
+      <c r="B15" s="214" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="215"/>
-      <c r="D15" s="216"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="215"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="215" t="s">
+      <c r="B16" s="214" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="215"/>
-      <c r="D16" s="216"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="215"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="215" t="s">
+      <c r="B17" s="214" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="215"/>
-      <c r="D17" s="216"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="215"/>
     </row>
     <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="207" t="s">
+      <c r="B18" s="206" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="208"/>
-      <c r="D18" s="209"/>
+      <c r="C18" s="207"/>
+      <c r="D18" s="208"/>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="207" t="s">
+      <c r="B19" s="206" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="208"/>
-      <c r="D19" s="209"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="208"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="207" t="s">
+      <c r="B20" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="209"/>
+      <c r="C20" s="207"/>
+      <c r="D20" s="208"/>
     </row>
     <row r="21" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="207" t="s">
+      <c r="B21" s="206" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="208"/>
-      <c r="D21" s="209"/>
+      <c r="C21" s="207"/>
+      <c r="D21" s="208"/>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="207" t="s">
+      <c r="B22" s="206" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="208"/>
-      <c r="D22" s="209"/>
+      <c r="C22" s="207"/>
+      <c r="D22" s="208"/>
     </row>
     <row r="23" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="207" t="s">
+      <c r="B23" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="208"/>
-      <c r="D23" s="209"/>
+      <c r="C23" s="207"/>
+      <c r="D23" s="208"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="207" t="s">
+      <c r="B24" s="206" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="208"/>
-      <c r="D24" s="209"/>
+      <c r="C24" s="207"/>
+      <c r="D24" s="208"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="207" t="s">
+      <c r="B25" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="208"/>
-      <c r="D25" s="209"/>
+      <c r="C25" s="207"/>
+      <c r="D25" s="208"/>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="207" t="s">
+      <c r="B26" s="206" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="208"/>
-      <c r="D26" s="209"/>
+      <c r="C26" s="207"/>
+      <c r="D26" s="208"/>
       <c r="F26" s="34"/>
     </row>
     <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="207" t="s">
+      <c r="B27" s="206" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="208"/>
-      <c r="D27" s="209"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="208"/>
       <c r="F27" s="35"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="207" t="s">
+      <c r="B28" s="206" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="208"/>
-      <c r="D28" s="209"/>
+      <c r="C28" s="207"/>
+      <c r="D28" s="208"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="215" t="s">
+      <c r="B29" s="214" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="215"/>
-      <c r="D29" s="216"/>
+      <c r="C29" s="214"/>
+      <c r="D29" s="215"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="215" t="s">
+      <c r="B30" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="215"/>
-      <c r="D30" s="216"/>
+      <c r="C30" s="214"/>
+      <c r="D30" s="215"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="217" t="s">
+      <c r="B31" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="217"/>
-      <c r="D31" s="218"/>
+      <c r="C31" s="216"/>
+      <c r="D31" s="217"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9592,37 +9567,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="234" t="s">
+      <c r="A2" s="233" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="234"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="234" t="s">
+      <c r="A3" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="234"/>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="234"/>
+      <c r="B3" s="233"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="233"/>
     </row>
     <row r="4" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="71" t="s">
